--- a/Employee_Reports_wi48/Roby Chua Malinao Q0613.xlsx
+++ b/Employee_Reports_wi48/Roby Chua Malinao Q0613.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1244,11 +1244,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1281,11 +1281,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1355,11 +1355,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
